--- a/research/traditional_assets/database/data/taiwan/taiwan_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09275</v>
+        <v>0.0211</v>
       </c>
       <c r="E2">
-        <v>0.0465</v>
+        <v>-0.04</v>
       </c>
       <c r="G2">
-        <v>0.06627417998317915</v>
+        <v>0.07765640516385303</v>
       </c>
       <c r="H2">
-        <v>0.06627417998317915</v>
+        <v>0.07765640516385303</v>
       </c>
       <c r="I2">
-        <v>0.1036844602268714</v>
+        <v>0.05998013902681231</v>
       </c>
       <c r="J2">
-        <v>0.07856082077021577</v>
+        <v>0.04885588137936406</v>
       </c>
       <c r="K2">
-        <v>10.45</v>
+        <v>5.19</v>
       </c>
       <c r="L2">
-        <v>0.04394449116904963</v>
+        <v>0.05153922542204568</v>
       </c>
       <c r="M2">
-        <v>5.39</v>
+        <v>4.71</v>
       </c>
       <c r="N2">
-        <v>0.04389250814332248</v>
+        <v>0.06728571428571428</v>
       </c>
       <c r="O2">
-        <v>0.5157894736842105</v>
+        <v>0.9075144508670521</v>
       </c>
       <c r="P2">
-        <v>5.39</v>
+        <v>4.71</v>
       </c>
       <c r="Q2">
-        <v>0.04389250814332248</v>
+        <v>0.06728571428571428</v>
       </c>
       <c r="R2">
-        <v>0.5157894736842105</v>
+        <v>0.9075144508670521</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>31.88</v>
+        <v>13.56</v>
       </c>
       <c r="V2">
-        <v>0.2596091205211726</v>
+        <v>0.1937142857142857</v>
       </c>
       <c r="W2">
-        <v>0.1521452145214522</v>
+        <v>0.1468088097469541</v>
       </c>
       <c r="X2">
-        <v>0.05262699320102242</v>
+        <v>0.08450361588752084</v>
       </c>
       <c r="Y2">
-        <v>0.09951822132042973</v>
+        <v>0.06230519385943323</v>
       </c>
       <c r="Z2">
-        <v>3.813392226133123</v>
+        <v>3.772948669913825</v>
       </c>
       <c r="AA2">
-        <v>0.2941915705385698</v>
+        <v>0.1934054385553987</v>
       </c>
       <c r="AB2">
-        <v>0.0482679776619513</v>
+        <v>0.08159192102168486</v>
       </c>
       <c r="AC2">
-        <v>0.2433483255294038</v>
+        <v>0.1118135175337138</v>
       </c>
       <c r="AD2">
-        <v>25.13</v>
+        <v>6.17</v>
       </c>
       <c r="AE2">
-        <v>9.46917679024989</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>34.59917679024989</v>
+        <v>6.17</v>
       </c>
       <c r="AG2">
-        <v>2.719176790249893</v>
+        <v>-7.389999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.2198180288856069</v>
+        <v>0.08100301956150716</v>
       </c>
       <c r="AI2">
-        <v>0.2487374662354947</v>
+        <v>0.1710562794566121</v>
       </c>
       <c r="AJ2">
-        <v>0.02166343709211702</v>
+        <v>-0.1180322632167385</v>
       </c>
       <c r="AK2">
-        <v>0.02536091836975533</v>
+        <v>-0.3282985339848956</v>
       </c>
       <c r="AL2">
-        <v>0.279</v>
+        <v>0.091</v>
       </c>
       <c r="AM2">
-        <v>-0.735</v>
+        <v>-0.382</v>
       </c>
       <c r="AN2">
-        <v>0.885794853718717</v>
+        <v>0.8955007256894049</v>
       </c>
       <c r="AO2">
-        <v>72.86738351254481</v>
+        <v>66.37362637362638</v>
       </c>
       <c r="AP2">
-        <v>0.09584690836270332</v>
+        <v>-1.072568940493469</v>
       </c>
       <c r="AQ2">
-        <v>-27.65986394557823</v>
+        <v>-15.81151832460733</v>
       </c>
     </row>
     <row r="3">
@@ -722,40 +722,40 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.05850931677018634</v>
+        <v>0.05790155440414507</v>
       </c>
       <c r="H3">
-        <v>0.05850931677018634</v>
+        <v>0.05790155440414507</v>
       </c>
       <c r="I3">
-        <v>0.04906832298136646</v>
+        <v>0.04740932642487047</v>
       </c>
       <c r="J3">
-        <v>0.03929230671474639</v>
+        <v>0.03827273914747246</v>
       </c>
       <c r="K3">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="L3">
-        <v>0.03900621118012423</v>
+        <v>0.03730569948186528</v>
       </c>
       <c r="M3">
-        <v>2.51</v>
+        <v>2.35</v>
       </c>
       <c r="N3">
-        <v>0.07254335260115606</v>
+        <v>0.07556270096463022</v>
       </c>
       <c r="O3">
-        <v>0.7993630573248407</v>
+        <v>0.8159722222222223</v>
       </c>
       <c r="P3">
-        <v>2.51</v>
+        <v>2.35</v>
       </c>
       <c r="Q3">
-        <v>0.07254335260115606</v>
+        <v>0.07556270096463022</v>
       </c>
       <c r="R3">
-        <v>0.7993630573248407</v>
+        <v>0.8159722222222223</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,73 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>11</v>
+        <v>10.7</v>
       </c>
       <c r="V3">
-        <v>0.3179190751445087</v>
+        <v>0.3440514469453376</v>
       </c>
       <c r="W3">
-        <v>0.247244094488189</v>
+        <v>0.1745454545454545</v>
       </c>
       <c r="X3">
-        <v>0.05262699320102242</v>
+        <v>0.08611652373360641</v>
       </c>
       <c r="Y3">
-        <v>0.1946171012871666</v>
+        <v>0.08842893081184812</v>
       </c>
       <c r="Z3">
-        <v>9.962871287128715</v>
+        <v>6.760070052539404</v>
       </c>
       <c r="AA3">
-        <v>0.3914641943734016</v>
+        <v>0.2587263977394811</v>
       </c>
       <c r="AB3">
-        <v>0.0482679776619513</v>
+        <v>0.08201685554972238</v>
       </c>
       <c r="AC3">
-        <v>0.3431962167114503</v>
+        <v>0.1767095421897587</v>
       </c>
       <c r="AD3">
-        <v>5.92</v>
+        <v>4.38</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5.92</v>
+        <v>4.38</v>
       </c>
       <c r="AG3">
-        <v>-5.08</v>
+        <v>-6.319999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.1461006910167818</v>
+        <v>0.1234498308906426</v>
       </c>
       <c r="AI3">
-        <v>0.264049955396967</v>
+        <v>0.2422566371681416</v>
       </c>
       <c r="AJ3">
-        <v>-0.1720867208672087</v>
+        <v>-0.2550443906376109</v>
       </c>
       <c r="AK3">
-        <v>-0.4448336252189142</v>
+        <v>-0.8563685636856367</v>
       </c>
       <c r="AL3">
-        <v>0.077</v>
+        <v>0.073</v>
       </c>
       <c r="AM3">
-        <v>0.06999999999999999</v>
+        <v>0.06599999999999999</v>
       </c>
       <c r="AN3">
-        <v>1.286956521739131</v>
+        <v>1.023364485981308</v>
       </c>
       <c r="AO3">
-        <v>51.2987012987013</v>
+        <v>50.13698630136987</v>
       </c>
       <c r="AP3">
-        <v>-1.104347826086957</v>
+        <v>-1.476635514018691</v>
       </c>
       <c r="AQ3">
-        <v>56.42857142857144</v>
+        <v>55.45454545454547</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>China United Insurance Service, Inc. (OTCPK:CUII)</t>
+          <t>Taiming Assurance Broker Co.,Ltd. (TPEX:5878)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,252 +850,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.154</v>
+        <v>0.0211</v>
       </c>
       <c r="E4">
-        <v>0.106</v>
+        <v>-0.04</v>
       </c>
       <c r="G4">
-        <v>0.05553822152886116</v>
+        <v>0.1425531914893617</v>
       </c>
       <c r="H4">
-        <v>0.05553822152886116</v>
+        <v>0.1425531914893617</v>
       </c>
       <c r="I4">
-        <v>0.1374895837905618</v>
+        <v>0.1012765957446808</v>
       </c>
       <c r="J4">
-        <v>0.09149123039004298</v>
+        <v>0.08322765957446808</v>
       </c>
       <c r="K4">
-        <v>4.61</v>
+        <v>2.31</v>
       </c>
       <c r="L4">
-        <v>0.0359594383775351</v>
+        <v>0.09829787234042553</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>2.36</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.06066838046272494</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>1.021645021645021</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>2.36</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.06066838046272494</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>1.021645021645021</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>18.2</v>
+        <v>2.86</v>
       </c>
       <c r="V4">
-        <v>0.4008810572687225</v>
+        <v>0.07352185089974293</v>
       </c>
       <c r="W4">
-        <v>0.1521452145214522</v>
+        <v>0.1190721649484536</v>
       </c>
       <c r="X4">
-        <v>0.06420264864645144</v>
+        <v>0.08289070804143525</v>
       </c>
       <c r="Y4">
-        <v>0.08794256587500072</v>
+        <v>0.03618145690701836</v>
       </c>
       <c r="Z4">
-        <v>3.21551660508204</v>
+        <v>1.538965291421087</v>
       </c>
       <c r="AA4">
-        <v>0.2941915705385698</v>
+        <v>0.1280844793713163</v>
       </c>
       <c r="AB4">
-        <v>0.05084324500916597</v>
+        <v>0.08116698649364734</v>
       </c>
       <c r="AC4">
-        <v>0.2433483255294038</v>
+        <v>0.04691749287766897</v>
       </c>
       <c r="AD4">
-        <v>18.2</v>
+        <v>1.79</v>
       </c>
       <c r="AE4">
-        <v>9.46917679024989</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>27.66917679024989</v>
+        <v>1.79</v>
       </c>
       <c r="AG4">
-        <v>9.46917679024989</v>
+        <v>-1.07</v>
       </c>
       <c r="AH4">
-        <v>0.3786709800998055</v>
+        <v>0.0439911526173507</v>
       </c>
       <c r="AI4">
-        <v>0.287414702325077</v>
+        <v>0.09949972206781546</v>
       </c>
       <c r="AJ4">
-        <v>0.1725773438600693</v>
+        <v>-0.02828443034628601</v>
       </c>
       <c r="AK4">
-        <v>0.1212921306406359</v>
+        <v>-0.07072042300066093</v>
       </c>
       <c r="AL4">
-        <v>0.185</v>
+        <v>0.018</v>
       </c>
       <c r="AM4">
-        <v>-0.5940000000000001</v>
+        <v>-0.448</v>
       </c>
       <c r="AN4">
-        <v>0.89128305582762</v>
+        <v>0.685823754789272</v>
       </c>
       <c r="AO4">
-        <v>71.8918918918919</v>
+        <v>132.2222222222222</v>
       </c>
       <c r="AP4">
-        <v>0.4637207047135108</v>
+        <v>-0.4099616858237548</v>
       </c>
       <c r="AQ4">
-        <v>-22.39057239057239</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Taiming Assurance Broker Co.,Ltd. (TPEX:5878)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.0315</v>
-      </c>
-      <c r="E5">
-        <v>-0.013</v>
-      </c>
-      <c r="G5">
-        <v>0.1350515463917526</v>
-      </c>
-      <c r="H5">
-        <v>0.1350515463917526</v>
-      </c>
-      <c r="I5">
-        <v>0.1058419243986254</v>
-      </c>
-      <c r="J5">
-        <v>0.08540021541775657</v>
-      </c>
-      <c r="K5">
-        <v>2.7</v>
-      </c>
-      <c r="L5">
-        <v>0.09278350515463918</v>
-      </c>
-      <c r="M5">
-        <v>2.88</v>
-      </c>
-      <c r="N5">
-        <v>0.06728971962616823</v>
-      </c>
-      <c r="O5">
-        <v>1.066666666666667</v>
-      </c>
-      <c r="P5">
-        <v>2.88</v>
-      </c>
-      <c r="Q5">
-        <v>0.06728971962616823</v>
-      </c>
-      <c r="R5">
-        <v>1.066666666666667</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>2.68</v>
-      </c>
-      <c r="V5">
-        <v>0.06261682242990654</v>
-      </c>
-      <c r="W5">
-        <v>0.1508379888268157</v>
-      </c>
-      <c r="X5">
-        <v>0.04873195181071941</v>
-      </c>
-      <c r="Y5">
-        <v>0.1021060370160963</v>
-      </c>
-      <c r="Z5">
-        <v>2.019430950728661</v>
-      </c>
-      <c r="AA5">
-        <v>0.1724598382135126</v>
-      </c>
-      <c r="AB5">
-        <v>0.0481339134785067</v>
-      </c>
-      <c r="AC5">
-        <v>0.1243259247350059</v>
-      </c>
-      <c r="AD5">
-        <v>1.01</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>1.01</v>
-      </c>
-      <c r="AG5">
-        <v>-1.67</v>
-      </c>
-      <c r="AH5">
-        <v>0.0230540972380735</v>
-      </c>
-      <c r="AI5">
-        <v>0.04948554630083293</v>
-      </c>
-      <c r="AJ5">
-        <v>-0.04060296620471676</v>
-      </c>
-      <c r="AK5">
-        <v>-0.09419063733784548</v>
-      </c>
-      <c r="AL5">
-        <v>0.017</v>
-      </c>
-      <c r="AM5">
-        <v>-0.211</v>
-      </c>
-      <c r="AN5">
-        <v>0.3014925373134328</v>
-      </c>
-      <c r="AO5">
-        <v>181.1764705882353</v>
-      </c>
-      <c r="AP5">
-        <v>-0.4985074626865672</v>
-      </c>
-      <c r="AQ5">
-        <v>-14.59715639810426</v>
+        <v>-5.3125</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/taiwan/taiwan_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_insurance_general.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0211</v>
+        <v>0.05705</v>
       </c>
       <c r="E2">
-        <v>-0.04</v>
+        <v>0.04079999999999999</v>
       </c>
       <c r="G2">
-        <v>0.07765640516385303</v>
+        <v>0.05522243713733075</v>
       </c>
       <c r="H2">
-        <v>0.07765640516385303</v>
+        <v>0.05522243713733075</v>
       </c>
       <c r="I2">
-        <v>0.05998013902681231</v>
+        <v>0.05067698259187621</v>
       </c>
       <c r="J2">
-        <v>0.04885588137936406</v>
+        <v>0.04085672025096306</v>
       </c>
       <c r="K2">
-        <v>5.19</v>
+        <v>4.42</v>
       </c>
       <c r="L2">
-        <v>0.05153922542204568</v>
+        <v>0.04274661508704061</v>
       </c>
       <c r="M2">
-        <v>4.71</v>
+        <v>6.27</v>
       </c>
       <c r="N2">
-        <v>0.06728571428571428</v>
+        <v>0.07367802585193889</v>
       </c>
       <c r="O2">
-        <v>0.9075144508670521</v>
+        <v>1.418552036199095</v>
       </c>
       <c r="P2">
-        <v>4.71</v>
+        <v>6.27</v>
       </c>
       <c r="Q2">
-        <v>0.06728571428571428</v>
+        <v>0.07367802585193889</v>
       </c>
       <c r="R2">
-        <v>0.9075144508670521</v>
+        <v>1.418552036199095</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>13.56</v>
+        <v>9.700000000000001</v>
       </c>
       <c r="V2">
-        <v>0.1937142857142857</v>
+        <v>0.1139835487661575</v>
       </c>
       <c r="W2">
-        <v>0.1468088097469541</v>
+        <v>0.1516828872668289</v>
       </c>
       <c r="X2">
-        <v>0.08450361588752084</v>
+        <v>0.07433043994518808</v>
       </c>
       <c r="Y2">
-        <v>0.06230519385943323</v>
+        <v>0.0773524473216408</v>
       </c>
       <c r="Z2">
-        <v>3.772948669913825</v>
+        <v>5.081081081081082</v>
       </c>
       <c r="AA2">
-        <v>0.1934054385553987</v>
+        <v>0.2425029895491805</v>
       </c>
       <c r="AB2">
-        <v>0.08159192102168486</v>
+        <v>0.07267347722056305</v>
       </c>
       <c r="AC2">
-        <v>0.1118135175337138</v>
+        <v>0.1698295123286175</v>
       </c>
       <c r="AD2">
-        <v>6.17</v>
+        <v>4.63</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6.17</v>
+        <v>4.63</v>
       </c>
       <c r="AG2">
-        <v>-7.389999999999999</v>
+        <v>-5.070000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.08100301956150716</v>
+        <v>0.05159924217095732</v>
       </c>
       <c r="AI2">
-        <v>0.1710562794566121</v>
+        <v>0.1333141376331702</v>
       </c>
       <c r="AJ2">
-        <v>-0.1180322632167385</v>
+        <v>-0.06335124328376861</v>
       </c>
       <c r="AK2">
-        <v>-0.3282985339848956</v>
+        <v>-0.2025569316819817</v>
       </c>
       <c r="AL2">
-        <v>0.091</v>
+        <v>0.077</v>
       </c>
       <c r="AM2">
-        <v>-0.382</v>
+        <v>-0.179</v>
       </c>
       <c r="AN2">
-        <v>0.8955007256894049</v>
+        <v>0.7627677100494233</v>
       </c>
       <c r="AO2">
-        <v>66.37362637362638</v>
+        <v>68.05194805194806</v>
       </c>
       <c r="AP2">
-        <v>-1.072568940493469</v>
+        <v>-0.8352553542009886</v>
       </c>
       <c r="AQ2">
-        <v>-15.81151832460733</v>
+        <v>-29.27374301675978</v>
       </c>
     </row>
     <row r="3">
@@ -721,41 +721,47 @@
           <t>Insurance (General)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.0964</v>
+      </c>
+      <c r="E3">
+        <v>0.141</v>
+      </c>
       <c r="G3">
-        <v>0.05790155440414507</v>
+        <v>0.04140526976160602</v>
       </c>
       <c r="H3">
-        <v>0.05790155440414507</v>
+        <v>0.04140526976160602</v>
       </c>
       <c r="I3">
-        <v>0.04740932642487047</v>
+        <v>0.04341279799247177</v>
       </c>
       <c r="J3">
-        <v>0.03827273914747246</v>
+        <v>0.03452594287401284</v>
       </c>
       <c r="K3">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="L3">
-        <v>0.03730569948186528</v>
+        <v>0.03400250941028858</v>
       </c>
       <c r="M3">
-        <v>2.35</v>
+        <v>4.17</v>
       </c>
       <c r="N3">
-        <v>0.07556270096463022</v>
+        <v>0.09025974025974025</v>
       </c>
       <c r="O3">
-        <v>0.8159722222222223</v>
+        <v>1.538745387453875</v>
       </c>
       <c r="P3">
-        <v>2.35</v>
+        <v>4.17</v>
       </c>
       <c r="Q3">
-        <v>0.07556270096463022</v>
+        <v>0.09025974025974025</v>
       </c>
       <c r="R3">
-        <v>0.8159722222222223</v>
+        <v>1.538745387453875</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>10.7</v>
+        <v>7.94</v>
       </c>
       <c r="V3">
-        <v>0.3440514469453376</v>
+        <v>0.1718614718614719</v>
       </c>
       <c r="W3">
-        <v>0.1745454545454545</v>
+        <v>0.1978102189781022</v>
       </c>
       <c r="X3">
-        <v>0.08611652373360641</v>
+        <v>0.07484469009297379</v>
       </c>
       <c r="Y3">
-        <v>0.08842893081184812</v>
+        <v>0.1229655288851284</v>
       </c>
       <c r="Z3">
-        <v>6.760070052539404</v>
+        <v>10.79945799457995</v>
       </c>
       <c r="AA3">
-        <v>0.2587263977394811</v>
+        <v>0.3728614697911686</v>
       </c>
       <c r="AB3">
-        <v>0.08201685554972238</v>
+        <v>0.07259928748353905</v>
       </c>
       <c r="AC3">
-        <v>0.1767095421897587</v>
+        <v>0.3002621823076295</v>
       </c>
       <c r="AD3">
-        <v>4.38</v>
+        <v>3.31</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4.38</v>
+        <v>3.31</v>
       </c>
       <c r="AG3">
-        <v>-6.319999999999999</v>
+        <v>-4.630000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.1234498308906426</v>
+        <v>0.0668551807715613</v>
       </c>
       <c r="AI3">
-        <v>0.2422566371681416</v>
+        <v>0.1923300406740267</v>
       </c>
       <c r="AJ3">
-        <v>-0.2550443906376109</v>
+        <v>-0.1113783978830888</v>
       </c>
       <c r="AK3">
-        <v>-0.8563685636856367</v>
+        <v>-0.499460625674218</v>
       </c>
       <c r="AL3">
-        <v>0.073</v>
+        <v>0.055</v>
       </c>
       <c r="AM3">
-        <v>0.06599999999999999</v>
+        <v>0.022</v>
       </c>
       <c r="AN3">
-        <v>1.023364485981308</v>
+        <v>0.8092909535452323</v>
       </c>
       <c r="AO3">
-        <v>50.13698630136987</v>
+        <v>62.90909090909091</v>
       </c>
       <c r="AP3">
-        <v>-1.476635514018691</v>
+        <v>-1.132029339853301</v>
       </c>
       <c r="AQ3">
-        <v>55.45454545454547</v>
+        <v>157.2727272727273</v>
       </c>
     </row>
     <row r="4">
@@ -850,46 +856,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0211</v>
+        <v>0.0177</v>
       </c>
       <c r="E4">
-        <v>-0.04</v>
+        <v>-0.0594</v>
       </c>
       <c r="G4">
-        <v>0.1425531914893617</v>
+        <v>0.1016877637130802</v>
       </c>
       <c r="H4">
-        <v>0.1425531914893617</v>
+        <v>0.1016877637130802</v>
       </c>
       <c r="I4">
-        <v>0.1012765957446808</v>
+        <v>0.07510548523206752</v>
       </c>
       <c r="J4">
-        <v>0.08322765957446808</v>
+        <v>0.06137191078963232</v>
       </c>
       <c r="K4">
-        <v>2.31</v>
+        <v>1.71</v>
       </c>
       <c r="L4">
-        <v>0.09829787234042553</v>
+        <v>0.07215189873417721</v>
       </c>
       <c r="M4">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="N4">
-        <v>0.06066838046272494</v>
+        <v>0.05398457583547558</v>
       </c>
       <c r="O4">
-        <v>1.021645021645021</v>
+        <v>1.228070175438597</v>
       </c>
       <c r="P4">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="Q4">
-        <v>0.06066838046272494</v>
+        <v>0.05398457583547558</v>
       </c>
       <c r="R4">
-        <v>1.021645021645021</v>
+        <v>1.228070175438597</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -898,73 +904,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2.86</v>
+        <v>1.76</v>
       </c>
       <c r="V4">
-        <v>0.07352185089974293</v>
+        <v>0.04524421593830334</v>
       </c>
       <c r="W4">
-        <v>0.1190721649484536</v>
+        <v>0.1055555555555556</v>
       </c>
       <c r="X4">
-        <v>0.08289070804143525</v>
+        <v>0.07381618979740237</v>
       </c>
       <c r="Y4">
-        <v>0.03618145690701836</v>
+        <v>0.03173936575815318</v>
       </c>
       <c r="Z4">
-        <v>1.538965291421087</v>
+        <v>1.827293754818813</v>
       </c>
       <c r="AA4">
-        <v>0.1280844793713163</v>
+        <v>0.1121445093071924</v>
       </c>
       <c r="AB4">
-        <v>0.08116698649364734</v>
+        <v>0.07274766695758707</v>
       </c>
       <c r="AC4">
-        <v>0.04691749287766897</v>
+        <v>0.03939684234960537</v>
       </c>
       <c r="AD4">
-        <v>1.79</v>
+        <v>1.32</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.79</v>
+        <v>1.32</v>
       </c>
       <c r="AG4">
-        <v>-1.07</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.0439911526173507</v>
+        <v>0.03281949278965689</v>
       </c>
       <c r="AI4">
-        <v>0.09949972206781546</v>
+        <v>0.07534246575342467</v>
       </c>
       <c r="AJ4">
-        <v>-0.02828443034628601</v>
+        <v>-0.01144045761830473</v>
       </c>
       <c r="AK4">
-        <v>-0.07072042300066093</v>
+        <v>-0.02791878172588832</v>
       </c>
       <c r="AL4">
-        <v>0.018</v>
+        <v>0.022</v>
       </c>
       <c r="AM4">
-        <v>-0.448</v>
+        <v>-0.201</v>
       </c>
       <c r="AN4">
-        <v>0.685823754789272</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="AO4">
-        <v>132.2222222222222</v>
+        <v>80.90909090909092</v>
       </c>
       <c r="AP4">
-        <v>-0.4099616858237548</v>
+        <v>-0.2222222222222222</v>
       </c>
       <c r="AQ4">
-        <v>-5.3125</v>
+        <v>-8.855721393034825</v>
       </c>
     </row>
   </sheetData>
